--- a/astro-site/public/dl/kit-tareas-chocolateria/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/03-tareas-manager.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Diario" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Semanal" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mensual" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diario" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semanal" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Diario'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Semanal'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mensual'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -81,6 +85,11 @@
       <name val="Calibri"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
@@ -151,57 +160,68 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -561,15 +581,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -577,6 +598,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -605,9 +627,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -629,8 +649,25 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -639,18 +676,18 @@
   <sheetPr>
     <tabColor rgb="00FFF8E1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -667,6 +704,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -806,6 +844,7 @@
       <c r="F10" s="11" t="n"/>
       <c r="G10" s="13" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
@@ -945,6 +984,7 @@
       <c r="F18" s="11" t="n"/>
       <c r="G18" s="13" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
@@ -1065,6 +1105,26 @@
       <c r="F25" s="11" t="n"/>
       <c r="G25" s="13" t="n"/>
     </row>
+    <row r="26">
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C26">
+        <f>COUNTIF(E6:E25,"✓")</f>
+        <v>2.0</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E26">
+        <f>COUNTIF(B6:B25,"?*")</f>
+        <v>16.0</v>
+      </c>
+    </row>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
         <is>
@@ -1082,19 +1142,33 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A27:G27"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G25">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E22 E23 E24 E25" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E22 E23 E24 E25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1103,18 +1177,18 @@
   <sheetPr>
     <tabColor rgb="00FFF8E1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,6 +1205,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1251,6 +1326,7 @@
       <c r="F9" s="11" t="n"/>
       <c r="G9" s="13" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -1352,6 +1428,7 @@
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="13" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -1453,6 +1530,7 @@
       <c r="F21" s="11" t="n"/>
       <c r="G21" s="13" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
@@ -1554,6 +1632,7 @@
       <c r="F27" s="11" t="n"/>
       <c r="G27" s="13" t="n"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
@@ -1673,6 +1752,26 @@
       <c r="E34" s="12" t="n"/>
       <c r="F34" s="11" t="n"/>
       <c r="G34" s="13" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C35">
+        <f>COUNTIF(E6:E34,"✓")</f>
+        <v>4.0</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E35">
+        <f>COUNTIF(B6:B34,"?*")</f>
+        <v>21.0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
@@ -1700,12 +1799,26 @@
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A29:G29"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G34">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E13 E14 E15 E19 E20 E21 E25 E26 E27 E31 E32 E33 E34" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E19 E20 E21 E25 E26 E27 E31 E32 E33 E34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1714,18 +1827,18 @@
   <sheetPr>
     <tabColor rgb="00FFF8E1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1742,6 +1855,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1862,6 +1976,7 @@
       <c r="F9" s="11" t="n"/>
       <c r="G9" s="13" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -1963,6 +2078,7 @@
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="13" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -2082,6 +2198,26 @@
       <c r="E22" s="12" t="n"/>
       <c r="F22" s="11" t="n"/>
       <c r="G22" s="13" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C23">
+        <f>COUNTIF(E6:E22,"✓")</f>
+        <v>2.0</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E23">
+        <f>COUNTIF(B6:B22,"?*")</f>
+        <v>13.0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
@@ -2107,11 +2243,25 @@
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G22">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E13 E14 E15 E19 E20 E21 E22" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E19 E20 E21 E22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-chocolateria/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/03-tareas-manager.xlsx
@@ -92,7 +92,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -135,6 +135,16 @@
         <bgColor rgb="00E0F7FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F8E9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -162,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -207,6 +217,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -583,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -651,9 +667,38 @@
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Obligaciones del encargado:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>▸ El registro de jornada se cierra y se valida CADA DÍA (obrador y tienda) y se archiva cada mes: es obligatorio desde el RD-ley 8/2019 y hay que conservarlo 4 años.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>▸ El bloque de fin de semana del «Semanal» existe porque en una chocolatería con tienda el sábado y el domingo son el pico de venta, y la planificación del lunes se hace con lo que allí se anota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -678,7 +723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1092,12 +1137,12 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Confirmar equipo y horarios de mañana</t>
+          <t>Cerrar y validar el registro diario de jornada de todo el equipo, obrador y tienda: es obligatorio (RD-ley 8/2019) y hay que conservarlo 4 años</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Equipo</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D25" s="11" t="n"/>
@@ -1106,57 +1151,76 @@
       <c r="G25" s="13" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="19" t="inlineStr">
+      <c r="A26" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Confirmar equipo y horarios de mañana</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="11" t="n"/>
+      <c r="G26" s="13" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C26">
-        <f>COUNTIF(E6:E25,"✓")</f>
-        <v>2.0</v>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C27">
+        <f>COUNTIFS(B6:B26,"?*",E6:E26,"✓")-COUNTIFS(B6:B26,"Tarea",E6:E26,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E26">
-        <f>COUNTIF(B6:B25,"?*")</f>
-        <v>16.0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
-        </is>
+      <c r="E27">
+        <f>COUNTIF(B6:B26,"?*")-COUNTIF(B6:B26,"Tarea")-COUNTIF(E6:E26,"N/A")</f>
+        <v>15.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
         <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A29:G29"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G25">
+  <conditionalFormatting sqref="A6:G26">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E22 E23 E24 E25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E22 E23 E24 E25 E26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1179,7 +1243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1753,60 +1817,163 @@
       <c r="F34" s="11" t="n"/>
       <c r="G34" s="13" t="n"/>
     </row>
-    <row r="35">
-      <c r="B35" s="19" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Sábado y domingo — Tienda a pleno</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Hora</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Reponer la vitrina antes de cada pico: media mañana y media tarde, sin esperar a que se vacíe</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>Vitrina</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="11" t="n"/>
+      <c r="G38" s="13" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Revisar el stock de packaging de regalo: cajas, lazos y bolsas se agotan el sábado y no hay proveedor hasta el lunes</t>
+        </is>
+      </c>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="11" t="n"/>
+      <c r="G39" s="13" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Anotar las roturas de stock y qué se dejó de vender, para la planificación del lunes</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Gestión</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="12" t="n"/>
+      <c r="F40" s="11" t="n"/>
+      <c r="G40" s="13" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C35">
-        <f>COUNTIF(E6:E34,"✓")</f>
-        <v>4.0</v>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="C41">
+        <f>COUNTIFS(B6:B40,"?*",E6:E40,"✓")-COUNTIFS(B6:B40,"Tarea",E6:E40,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E35">
-        <f>COUNTIF(B6:B34,"?*")</f>
-        <v>21.0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="E41">
+        <f>COUNTIF(B6:B40,"?*")-COUNTIF(B6:B40,"Tarea")-COUNTIF(E6:E40,"N/A")</f>
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>Firma responsable: _________________  Fecha: ___/___/______</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A37:G37"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A43:G43"/>
     <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A42:G42"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G34">
+  <conditionalFormatting sqref="A6:G40">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E19 E20 E21 E25 E26 E27 E31 E32 E33 E34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E19 E20 E21 E25 E26 E27 E31 E32 E33 E34 E38 E39 E40" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1829,7 +1996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2078,82 +2245,82 @@
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="13" t="n"/>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Archivar los registros de jornada del mes firmados y guardarlos a disposición de la Inspección de Trabajo (4 años)</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="13" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Producto y marketing</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Lanzar nuevo producto o sabor del mes</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>Producción</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="13" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Actualizar carta y etiquetado si hay cambios</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="inlineStr">
-        <is>
-          <t>Tienda</t>
+          <t>Lanzar nuevo producto o sabor del mes</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Producción</t>
         </is>
       </c>
       <c r="D20" s="11" t="n"/>
@@ -2163,16 +2330,16 @@
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Planificar contenido RRSS del mes siguiente</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>RRSS</t>
+          <t>Actualizar carta y etiquetado si hay cambios</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="D21" s="11" t="n"/>
@@ -2182,11 +2349,11 @@
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Revisar Google Reviews y responder pendientes</t>
+          <t>Planificar contenido RRSS del mes siguiente</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -2200,34 +2367,53 @@
       <c r="G22" s="13" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="19" t="inlineStr">
+      <c r="A23" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Revisar Google Reviews y responder pendientes</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>RRSS</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="11" t="n"/>
+      <c r="G23" s="13" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C23">
-        <f>COUNTIF(E6:E22,"✓")</f>
-        <v>2.0</v>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24">
+        <f>COUNTIFS(B6:B23,"?*",E6:E23,"✓")-COUNTIFS(B6:B23,"Tarea",E6:E23,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E23">
-        <f>COUNTIF(B6:B22,"?*")</f>
-        <v>13.0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
-        </is>
+      <c r="E24">
+        <f>COUNTIF(B6:B23,"?*")-COUNTIF(B6:B23,"Tarea")-COUNTIF(E6:E23,"N/A")</f>
+        <v>12.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
@@ -2237,20 +2423,20 @@
   <mergeCells count="7">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A26:G26"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G22">
+  <conditionalFormatting sqref="A6:G23">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E19 E20 E21 E22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E20 E21 E22 E23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/kit-tareas-chocolateria/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/03-tareas-manager.xlsx
@@ -599,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1207,8 +1207,8 @@
   <mergeCells count="7">
     <mergeCell ref="A28:G28"/>
     <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A29:G29"/>
@@ -1956,9 +1956,9 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A23:G23"/>
@@ -2423,8 +2423,8 @@
   <mergeCells count="7">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A26:G26"/>
